--- a/Assets/Document/云熹约定项目文档/9.事件配置表/特殊事件配置表/特殊事件配置表.xlsx
+++ b/Assets/Document/云熹约定项目文档/9.事件配置表/特殊事件配置表/特殊事件配置表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="66">
   <si>
     <t>描述</t>
   </si>
@@ -216,6 +216,15 @@
   </si>
   <si>
     <t>温叙事件五</t>
+  </si>
+  <si>
+    <t>陈予宁事件一</t>
+  </si>
+  <si>
+    <t>陈予荣事件一</t>
+  </si>
+  <si>
+    <t>何行舟事件一</t>
   </si>
 </sst>
 </file>
@@ -1363,7 +1372,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="3" width="8.875" customWidth="1"/>
@@ -1873,6 +1882,66 @@
         <v>62</v>
       </c>
     </row>
+    <row r="23" spans="2:10">
+      <c r="B23">
+        <v>20</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23">
+        <v>2</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J23" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10">
+      <c r="B24">
+        <v>21</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24">
+        <v>2</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10">
+      <c r="B25">
+        <v>22</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J25" t="s">
+        <v>65</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/Assets/Document/云熹约定项目文档/9.事件配置表/特殊事件配置表/特殊事件配置表.xlsx
+++ b/Assets/Document/云熹约定项目文档/9.事件配置表/特殊事件配置表/特殊事件配置表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="14580" windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -107,7 +107,7 @@
     <t>02</t>
   </si>
   <si>
-    <t>Shoppingmall</t>
+    <t>ShoppingMall</t>
   </si>
   <si>
     <t>03</t>
@@ -125,13 +125,13 @@
     <t>05</t>
   </si>
   <si>
-    <t>Bookstore</t>
+    <t>BookStore</t>
   </si>
   <si>
     <t>06</t>
   </si>
   <si>
-    <t>Amusement park</t>
+    <t>AmusementPark</t>
   </si>
   <si>
     <t>07</t>
@@ -143,13 +143,13 @@
     <t>08</t>
   </si>
   <si>
-    <t>Nail salon</t>
+    <t>NailSalon</t>
   </si>
   <si>
     <t>09</t>
   </si>
   <si>
-    <t>Barbershop</t>
+    <t>BarberShop</t>
   </si>
   <si>
     <t>周杉事件一</t>

--- a/Assets/Document/云熹约定项目文档/9.事件配置表/特殊事件配置表/特殊事件配置表.xlsx
+++ b/Assets/Document/云熹约定项目文档/9.事件配置表/特殊事件配置表/特殊事件配置表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="74">
   <si>
     <t>描述</t>
   </si>
@@ -41,7 +41,7 @@
     <t>事件类型</t>
   </si>
   <si>
-    <t>标题（文本）</t>
+    <t>陈予荣事件一</t>
   </si>
   <si>
     <t>消耗AP</t>
@@ -101,67 +101,97 @@
     <t>01</t>
   </si>
   <si>
+    <t>居家</t>
+  </si>
+  <si>
     <t>Home</t>
   </si>
   <si>
     <t>02</t>
   </si>
   <si>
+    <t>去商场</t>
+  </si>
+  <si>
     <t>ShoppingMall</t>
   </si>
   <si>
     <t>03</t>
   </si>
   <si>
+    <t>去医院</t>
+  </si>
+  <si>
     <t>Hospital</t>
   </si>
   <si>
     <t>04</t>
   </si>
   <si>
+    <t>去公园</t>
+  </si>
+  <si>
     <t>Park</t>
   </si>
   <si>
     <t>05</t>
   </si>
   <si>
+    <t>去书店</t>
+  </si>
+  <si>
     <t>BookStore</t>
   </si>
   <si>
     <t>06</t>
   </si>
   <si>
+    <t>去游乐园</t>
+  </si>
+  <si>
     <t>AmusementPark</t>
   </si>
   <si>
     <t>07</t>
   </si>
   <si>
+    <t>去电影院</t>
+  </si>
+  <si>
     <t>Cinema</t>
   </si>
   <si>
     <t>08</t>
   </si>
   <si>
+    <t>去美甲店</t>
+  </si>
+  <si>
     <t>NailSalon</t>
   </si>
   <si>
     <t>09</t>
   </si>
   <si>
+    <t>去理发店</t>
+  </si>
+  <si>
     <t>BarberShop</t>
   </si>
   <si>
     <t>周杉事件一</t>
   </si>
   <si>
+    <t>周杉事件二</t>
+  </si>
+  <si>
     <t>1|3|1</t>
   </si>
   <si>
     <t>2|12|1</t>
   </si>
   <si>
-    <t>周杉事件二</t>
+    <t>周杉事件三</t>
   </si>
   <si>
     <t>1|3|2</t>
@@ -170,7 +200,7 @@
     <t>2|18|1</t>
   </si>
   <si>
-    <t>周杉事件三</t>
+    <t>周杉事件四</t>
   </si>
   <si>
     <t>1|3|3</t>
@@ -179,7 +209,7 @@
     <t>2|24|1</t>
   </si>
   <si>
-    <t>周杉事件四</t>
+    <t>周杉事件五</t>
   </si>
   <si>
     <t>1|3|4</t>
@@ -188,40 +218,34 @@
     <t>2|30|1</t>
   </si>
   <si>
-    <t>周杉事件五</t>
-  </si>
-  <si>
     <t>温叙事件一</t>
   </si>
   <si>
+    <t>温叙事件二</t>
+  </si>
+  <si>
     <t>1|6|1</t>
   </si>
   <si>
-    <t>温叙事件二</t>
+    <t>温叙事件三</t>
   </si>
   <si>
     <t>1|6|2</t>
   </si>
   <si>
-    <t>温叙事件三</t>
+    <t>温叙事件四</t>
   </si>
   <si>
     <t>1|6|3</t>
   </si>
   <si>
-    <t>温叙事件四</t>
+    <t>温叙事件五</t>
   </si>
   <si>
     <t>1|6|4</t>
   </si>
   <si>
-    <t>温叙事件五</t>
-  </si>
-  <si>
     <t>陈予宁事件一</t>
-  </si>
-  <si>
-    <t>陈予荣事件一</t>
   </si>
   <si>
     <t>何行舟事件一</t>
@@ -1491,11 +1515,14 @@
       <c r="D4">
         <v>1</v>
       </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1503,16 +1530,19 @@
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
+      <c r="E5" t="s">
+        <v>27</v>
+      </c>
       <c r="F5">
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1520,16 +1550,19 @@
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
+      <c r="E6" t="s">
+        <v>30</v>
+      </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1537,16 +1570,19 @@
         <v>4</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
+      <c r="E7" t="s">
+        <v>33</v>
+      </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1554,16 +1590,19 @@
         <v>5</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
+      <c r="E8" t="s">
+        <v>36</v>
+      </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="J8" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1571,16 +1610,19 @@
         <v>6</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
+      <c r="E9" t="s">
+        <v>39</v>
+      </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1588,16 +1630,19 @@
         <v>7</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
+      <c r="E10" t="s">
+        <v>42</v>
+      </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -1605,16 +1650,19 @@
         <v>8</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
+      <c r="E11" t="s">
+        <v>45</v>
+      </c>
       <c r="F11">
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -1622,16 +1670,19 @@
         <v>9</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
+      <c r="E12" t="s">
+        <v>48</v>
+      </c>
       <c r="F12">
         <v>1</v>
       </c>
       <c r="J12" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -1644,14 +1695,17 @@
       <c r="D13">
         <v>2</v>
       </c>
+      <c r="E13" t="s">
+        <v>50</v>
+      </c>
       <c r="F13">
         <v>1</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J13" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -1659,25 +1713,28 @@
         <v>11</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D14">
         <v>2</v>
       </c>
+      <c r="E14" t="s">
+        <v>51</v>
+      </c>
       <c r="F14">
         <v>1</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H14" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="I14" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="J14" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1685,25 +1742,28 @@
         <v>12</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D15">
         <v>2</v>
       </c>
+      <c r="E15" t="s">
+        <v>54</v>
+      </c>
       <c r="F15">
         <v>1</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H15" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="I15" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="J15" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -1716,20 +1776,23 @@
       <c r="D16">
         <v>2</v>
       </c>
+      <c r="E16" t="s">
+        <v>57</v>
+      </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H16" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="I16" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="J16" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="2:10">
@@ -1737,25 +1800,28 @@
         <v>14</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D17">
         <v>2</v>
       </c>
+      <c r="E17" t="s">
+        <v>60</v>
+      </c>
       <c r="F17">
         <v>1</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H17" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="I17" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="J17" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="2:10">
@@ -1763,19 +1829,22 @@
         <v>15</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D18">
         <v>2</v>
       </c>
+      <c r="E18" t="s">
+        <v>63</v>
+      </c>
       <c r="F18">
         <v>1</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J18" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="2:10">
@@ -1783,25 +1852,28 @@
         <v>16</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D19">
         <v>2</v>
       </c>
+      <c r="E19" t="s">
+        <v>64</v>
+      </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H19" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="I19" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="J19" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="2:10">
@@ -1814,20 +1886,23 @@
       <c r="D20">
         <v>2</v>
       </c>
+      <c r="E20" t="s">
+        <v>66</v>
+      </c>
       <c r="F20">
         <v>1</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H20" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="I20" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="J20" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="2:10">
@@ -1835,25 +1910,28 @@
         <v>18</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D21">
         <v>2</v>
       </c>
+      <c r="E21" t="s">
+        <v>68</v>
+      </c>
       <c r="F21">
         <v>1</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I21" t="s">
         <v>59</v>
       </c>
-      <c r="I21" t="s">
-        <v>49</v>
-      </c>
       <c r="J21" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="2:10">
@@ -1861,25 +1939,28 @@
         <v>19</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D22">
         <v>2</v>
       </c>
+      <c r="E22" t="s">
+        <v>70</v>
+      </c>
       <c r="F22">
         <v>1</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H22" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="I22" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="J22" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="2:10">
@@ -1887,19 +1968,22 @@
         <v>20</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D23">
         <v>2</v>
       </c>
+      <c r="E23" t="s">
+        <v>72</v>
+      </c>
       <c r="F23">
         <v>1</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J23" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="2:10">
@@ -1907,19 +1991,22 @@
         <v>21</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D24">
         <v>2</v>
       </c>
+      <c r="E24" t="s">
+        <v>4</v>
+      </c>
       <c r="F24">
         <v>1</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J24" t="s">
-        <v>64</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="2:10">
@@ -1927,19 +2014,22 @@
         <v>22</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D25">
         <v>2</v>
       </c>
+      <c r="E25" t="s">
+        <v>73</v>
+      </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J25" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Document/云熹约定项目文档/9.事件配置表/特殊事件配置表/特殊事件配置表.xlsx
+++ b/Assets/Document/云熹约定项目文档/9.事件配置表/特殊事件配置表/特殊事件配置表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="87">
   <si>
     <t>描述</t>
   </si>
@@ -47,7 +47,7 @@
     <t>消耗AP</t>
   </si>
   <si>
-    <t>要求NPC_ID</t>
+    <t>事件标号</t>
   </si>
   <si>
     <t>是否会显示（解锁条件）</t>
@@ -77,7 +77,7 @@
     <t>CostAP</t>
   </si>
   <si>
-    <t>ReqNpcId</t>
+    <t>EventNum</t>
   </si>
   <si>
     <t>VisibleConditions</t>
@@ -182,9 +182,15 @@
     <t>周杉事件一</t>
   </si>
   <si>
+    <t>3_1</t>
+  </si>
+  <si>
     <t>周杉事件二</t>
   </si>
   <si>
+    <t>3_2</t>
+  </si>
+  <si>
     <t>1|3|1</t>
   </si>
   <si>
@@ -194,6 +200,9 @@
     <t>周杉事件三</t>
   </si>
   <si>
+    <t>3_3</t>
+  </si>
+  <si>
     <t>1|3|2</t>
   </si>
   <si>
@@ -203,6 +212,9 @@
     <t>周杉事件四</t>
   </si>
   <si>
+    <t>3_4</t>
+  </si>
+  <si>
     <t>1|3|3</t>
   </si>
   <si>
@@ -212,6 +224,9 @@
     <t>周杉事件五</t>
   </si>
   <si>
+    <t>3_5</t>
+  </si>
+  <si>
     <t>1|3|4</t>
   </si>
   <si>
@@ -221,34 +236,58 @@
     <t>温叙事件一</t>
   </si>
   <si>
+    <t>6_1</t>
+  </si>
+  <si>
     <t>温叙事件二</t>
   </si>
   <si>
+    <t>6_2</t>
+  </si>
+  <si>
     <t>1|6|1</t>
   </si>
   <si>
     <t>温叙事件三</t>
   </si>
   <si>
+    <t>6_3</t>
+  </si>
+  <si>
     <t>1|6|2</t>
   </si>
   <si>
     <t>温叙事件四</t>
   </si>
   <si>
+    <t>6_4</t>
+  </si>
+  <si>
     <t>1|6|3</t>
   </si>
   <si>
     <t>温叙事件五</t>
   </si>
   <si>
+    <t>6_5</t>
+  </si>
+  <si>
     <t>1|6|4</t>
   </si>
   <si>
     <t>陈予宁事件一</t>
   </si>
   <si>
+    <t>4_1</t>
+  </si>
+  <si>
+    <t>5_1</t>
+  </si>
+  <si>
     <t>何行舟事件一</t>
+  </si>
+  <si>
+    <t>7_1</t>
   </si>
 </sst>
 </file>
@@ -1493,7 +1532,7 @@
         <v>21</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s">
         <v>22</v>
@@ -1701,8 +1740,8 @@
       <c r="F13">
         <v>1</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>29</v>
+      <c r="G13" t="s">
+        <v>51</v>
       </c>
       <c r="J13" t="s">
         <v>50</v>
@@ -1719,22 +1758,22 @@
         <v>2</v>
       </c>
       <c r="E14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
-      <c r="G14" s="1" t="s">
-        <v>29</v>
+      <c r="G14" t="s">
+        <v>53</v>
       </c>
       <c r="H14" t="s">
+        <v>54</v>
+      </c>
+      <c r="I14" t="s">
+        <v>55</v>
+      </c>
+      <c r="J14" t="s">
         <v>52</v>
-      </c>
-      <c r="I14" t="s">
-        <v>53</v>
-      </c>
-      <c r="J14" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -1748,22 +1787,22 @@
         <v>2</v>
       </c>
       <c r="E15" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
-      <c r="G15" s="1" t="s">
-        <v>29</v>
+      <c r="G15" t="s">
+        <v>57</v>
       </c>
       <c r="H15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I15" t="s">
+        <v>59</v>
+      </c>
+      <c r="J15" t="s">
         <v>56</v>
-      </c>
-      <c r="J15" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -1777,22 +1816,22 @@
         <v>2</v>
       </c>
       <c r="E16" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>29</v>
+      <c r="G16" t="s">
+        <v>61</v>
       </c>
       <c r="H16" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="I16" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J16" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="2:10">
@@ -1806,22 +1845,22 @@
         <v>2</v>
       </c>
       <c r="E17" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
-      <c r="G17" s="1" t="s">
-        <v>29</v>
+      <c r="G17" t="s">
+        <v>65</v>
       </c>
       <c r="H17" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="I17" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="J17" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="2:10">
@@ -1835,16 +1874,16 @@
         <v>2</v>
       </c>
       <c r="E18" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F18">
         <v>1</v>
       </c>
-      <c r="G18" s="1" t="s">
-        <v>38</v>
+      <c r="G18" t="s">
+        <v>69</v>
       </c>
       <c r="J18" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="2:10">
@@ -1858,22 +1897,22 @@
         <v>2</v>
       </c>
       <c r="E19" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>38</v>
+      <c r="G19" t="s">
+        <v>71</v>
       </c>
       <c r="H19" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="I19" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J19" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="2:10">
@@ -1887,22 +1926,22 @@
         <v>2</v>
       </c>
       <c r="E20" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
-      <c r="G20" s="1" t="s">
-        <v>38</v>
+      <c r="G20" t="s">
+        <v>74</v>
       </c>
       <c r="H20" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="I20" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J20" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="2:10">
@@ -1916,22 +1955,22 @@
         <v>2</v>
       </c>
       <c r="E21" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="F21">
         <v>1</v>
       </c>
-      <c r="G21" s="1" t="s">
-        <v>38</v>
+      <c r="G21" t="s">
+        <v>77</v>
       </c>
       <c r="H21" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="I21" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J21" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="2:10">
@@ -1945,22 +1984,22 @@
         <v>2</v>
       </c>
       <c r="E22" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="F22">
         <v>1</v>
       </c>
-      <c r="G22" s="1" t="s">
-        <v>38</v>
+      <c r="G22" t="s">
+        <v>80</v>
       </c>
       <c r="H22" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="I22" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="J22" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="2:10">
@@ -1974,16 +2013,16 @@
         <v>2</v>
       </c>
       <c r="E23" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="F23">
         <v>1</v>
       </c>
-      <c r="G23" s="1" t="s">
-        <v>32</v>
+      <c r="G23" t="s">
+        <v>83</v>
       </c>
       <c r="J23" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" spans="2:10">
@@ -2002,8 +2041,8 @@
       <c r="F24">
         <v>1</v>
       </c>
-      <c r="G24" s="1" t="s">
-        <v>35</v>
+      <c r="G24" t="s">
+        <v>84</v>
       </c>
       <c r="J24" t="s">
         <v>4</v>
@@ -2020,16 +2059,16 @@
         <v>2</v>
       </c>
       <c r="E25" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
-      <c r="G25" s="1" t="s">
-        <v>41</v>
+      <c r="G25" t="s">
+        <v>86</v>
       </c>
       <c r="J25" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Document/云熹约定项目文档/9.事件配置表/特殊事件配置表/特殊事件配置表.xlsx
+++ b/Assets/Document/云熹约定项目文档/9.事件配置表/特殊事件配置表/特殊事件配置表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14580" windowHeight="17655"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="107">
   <si>
     <t>描述</t>
   </si>
@@ -104,6 +104,9 @@
     <t>居家</t>
   </si>
   <si>
+    <t>-1_1</t>
+  </si>
+  <si>
     <t>Home</t>
   </si>
   <si>
@@ -113,6 +116,9 @@
     <t>去商场</t>
   </si>
   <si>
+    <t>-1_2</t>
+  </si>
+  <si>
     <t>ShoppingMall</t>
   </si>
   <si>
@@ -122,6 +128,9 @@
     <t>去医院</t>
   </si>
   <si>
+    <t>-1_4</t>
+  </si>
+  <si>
     <t>Hospital</t>
   </si>
   <si>
@@ -131,6 +140,9 @@
     <t>去公园</t>
   </si>
   <si>
+    <t>-1_5</t>
+  </si>
+  <si>
     <t>Park</t>
   </si>
   <si>
@@ -140,6 +152,9 @@
     <t>去书店</t>
   </si>
   <si>
+    <t>-1_6</t>
+  </si>
+  <si>
     <t>BookStore</t>
   </si>
   <si>
@@ -149,6 +164,9 @@
     <t>去游乐园</t>
   </si>
   <si>
+    <t>-1_7</t>
+  </si>
+  <si>
     <t>AmusementPark</t>
   </si>
   <si>
@@ -158,6 +176,9 @@
     <t>去电影院</t>
   </si>
   <si>
+    <t>-1_8</t>
+  </si>
+  <si>
     <t>Cinema</t>
   </si>
   <si>
@@ -167,6 +188,9 @@
     <t>去美甲店</t>
   </si>
   <si>
+    <t>-1_9</t>
+  </si>
+  <si>
     <t>NailSalon</t>
   </si>
   <si>
@@ -176,6 +200,9 @@
     <t>去理发店</t>
   </si>
   <si>
+    <t>-1_10</t>
+  </si>
+  <si>
     <t>BarberShop</t>
   </si>
   <si>
@@ -288,6 +315,39 @@
   </si>
   <si>
     <t>7_1</t>
+  </si>
+  <si>
+    <t>现象级造梦师</t>
+  </si>
+  <si>
+    <t>0_1</t>
+  </si>
+  <si>
+    <t>3|80|3</t>
+  </si>
+  <si>
+    <t>传媒界的“无冕之王”</t>
+  </si>
+  <si>
+    <t>0_2</t>
+  </si>
+  <si>
+    <t>4|100|3</t>
+  </si>
+  <si>
+    <t>手握资本的“公关女王”</t>
+  </si>
+  <si>
+    <t>0_3</t>
+  </si>
+  <si>
+    <t>2|100|3</t>
+  </si>
+  <si>
+    <t>不被定义的自由</t>
+  </si>
+  <si>
+    <t>0_4</t>
   </si>
 </sst>
 </file>
@@ -903,11 +963,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1435,17 +1501,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="3" width="8.875" customWidth="1"/>
     <col min="4" max="4" width="10.375" customWidth="1"/>
-    <col min="5" max="5" width="12.875" customWidth="1"/>
+    <col min="5" max="5" width="21.25" customWidth="1"/>
     <col min="6" max="6" width="7.375" customWidth="1"/>
-    <col min="7" max="7" width="11.25" customWidth="1"/>
+    <col min="7" max="7" width="11.25" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.375" customWidth="1"/>
     <col min="9" max="9" width="20.375" customWidth="1"/>
-    <col min="10" max="10" width="17.125" customWidth="1"/>
+    <col min="10" max="10" width="21.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1467,7 +1533,7 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="H1" t="s">
@@ -1499,7 +1565,7 @@
       <c r="F2" t="s">
         <v>15</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1" t="s">
         <v>16</v>
       </c>
       <c r="H2" t="s">
@@ -1531,7 +1597,7 @@
       <c r="F3" t="s">
         <v>21</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H3" t="s">
@@ -1548,7 +1614,7 @@
       <c r="B4">
         <v>1</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D4">
@@ -1560,477 +1626,504 @@
       <c r="F4">
         <v>1</v>
       </c>
+      <c r="G4" s="3" t="s">
+        <v>25</v>
+      </c>
       <c r="J4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="B5">
         <v>2</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>26</v>
+      <c r="C5" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
+      <c r="G5" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="J5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="B6">
         <v>3</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>29</v>
+      <c r="C6" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
+      <c r="G6" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="J6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="B7">
         <v>4</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>32</v>
+      <c r="C7" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
+      <c r="G7" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="J7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="B8">
         <v>5</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>35</v>
+      <c r="C8" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
+      <c r="G8" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="J8" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="B9">
         <v>6</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>38</v>
+      <c r="C9" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
+      <c r="G9" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="J9" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="B10">
         <v>7</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>41</v>
+      <c r="C10" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
+      <c r="G10" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="J10" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="B11">
         <v>8</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>44</v>
+      <c r="C11" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F11">
         <v>1</v>
       </c>
+      <c r="G11" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="J11" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="B12">
         <v>9</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>47</v>
+      <c r="C12" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
+      <c r="G12" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="J12" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="B13">
         <v>10</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D13">
         <v>2</v>
       </c>
       <c r="E13" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="F13">
         <v>1</v>
       </c>
-      <c r="G13" t="s">
-        <v>51</v>
+      <c r="G13" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="J13" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="B14">
         <v>11</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>29</v>
+      <c r="C14" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="D14">
         <v>2</v>
       </c>
       <c r="E14" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
-      <c r="G14" t="s">
-        <v>53</v>
+      <c r="G14" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="H14" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="I14" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="J14" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="B15">
         <v>12</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>32</v>
+      <c r="C15" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="D15">
         <v>2</v>
       </c>
       <c r="E15" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
-      <c r="G15" t="s">
-        <v>57</v>
+      <c r="G15" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="H15" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="I15" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="J15" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="B16">
         <v>13</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D16">
         <v>2</v>
       </c>
       <c r="E16" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
-      <c r="G16" t="s">
-        <v>61</v>
+      <c r="G16" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="H16" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="I16" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="J16" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="2:10">
       <c r="B17">
         <v>14</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>38</v>
+      <c r="C17" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="D17">
         <v>2</v>
       </c>
       <c r="E17" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
-      <c r="G17" t="s">
-        <v>65</v>
+      <c r="G17" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="H17" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="I17" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="J17" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="2:10">
       <c r="B18">
         <v>15</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>35</v>
+      <c r="C18" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="D18">
         <v>2</v>
       </c>
       <c r="E18" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="F18">
         <v>1</v>
       </c>
-      <c r="G18" t="s">
-        <v>69</v>
+      <c r="G18" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="J18" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="2:10">
       <c r="B19">
         <v>16</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>26</v>
+      <c r="C19" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="D19">
         <v>2</v>
       </c>
       <c r="E19" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
-      <c r="G19" t="s">
-        <v>71</v>
+      <c r="G19" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="H19" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="I19" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="J19" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="2:10">
       <c r="B20">
         <v>17</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D20">
         <v>2</v>
       </c>
       <c r="E20" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
-      <c r="G20" t="s">
-        <v>74</v>
+      <c r="G20" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="H20" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="I20" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="J20" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" spans="2:10">
       <c r="B21">
         <v>18</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>29</v>
+      <c r="C21" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="D21">
         <v>2</v>
       </c>
       <c r="E21" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F21">
         <v>1</v>
       </c>
-      <c r="G21" t="s">
-        <v>77</v>
+      <c r="G21" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="H21" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="I21" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="J21" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="2:10">
       <c r="B22">
         <v>19</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>32</v>
+      <c r="C22" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="D22">
         <v>2</v>
       </c>
       <c r="E22" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F22">
         <v>1</v>
       </c>
-      <c r="G22" t="s">
-        <v>80</v>
+      <c r="G22" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="H22" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I22" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="J22" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="2:10">
       <c r="B23">
         <v>20</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>32</v>
+      <c r="C23" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="D23">
         <v>2</v>
       </c>
       <c r="E23" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="F23">
         <v>1</v>
       </c>
-      <c r="G23" t="s">
-        <v>83</v>
+      <c r="G23" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="J23" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="2:10">
       <c r="B24">
         <v>21</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>26</v>
+      <c r="C24" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="D24">
         <v>2</v>
@@ -2041,8 +2134,8 @@
       <c r="F24">
         <v>1</v>
       </c>
-      <c r="G24" t="s">
-        <v>84</v>
+      <c r="G24" s="1" t="s">
+        <v>93</v>
       </c>
       <c r="J24" t="s">
         <v>4</v>
@@ -2052,23 +2145,126 @@
       <c r="B25">
         <v>22</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>41</v>
+      <c r="C25" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="D25">
         <v>2</v>
       </c>
       <c r="E25" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
-      <c r="G25" t="s">
-        <v>86</v>
+      <c r="G25" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="J25" t="s">
-        <v>85</v>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10">
+      <c r="B26">
+        <v>23</v>
+      </c>
+      <c r="D26">
+        <v>3</v>
+      </c>
+      <c r="E26" t="s">
+        <v>96</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H26" t="s">
+        <v>98</v>
+      </c>
+      <c r="J26" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10">
+      <c r="B27">
+        <v>24</v>
+      </c>
+      <c r="D27">
+        <v>3</v>
+      </c>
+      <c r="E27" t="s">
+        <v>99</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="H27" t="s">
+        <v>101</v>
+      </c>
+      <c r="J27" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10">
+      <c r="B28">
+        <v>25</v>
+      </c>
+      <c r="D28">
+        <v>3</v>
+      </c>
+      <c r="E28" t="s">
+        <v>102</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H28" t="s">
+        <v>104</v>
+      </c>
+      <c r="J28" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10">
+      <c r="B29">
+        <v>26</v>
+      </c>
+      <c r="D29">
+        <v>3</v>
+      </c>
+      <c r="E29" t="s">
+        <v>105</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H29">
+        <v>7</v>
+      </c>
+      <c r="J29" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10">
+      <c r="B30">
+        <v>27</v>
+      </c>
+      <c r="D30">
+        <v>3</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Document/云熹约定项目文档/9.事件配置表/特殊事件配置表/特殊事件配置表.xlsx
+++ b/Assets/Document/云熹约定项目文档/9.事件配置表/特殊事件配置表/特殊事件配置表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="110">
   <si>
     <t>描述</t>
   </si>
@@ -221,7 +221,7 @@
     <t>1|3|1</t>
   </si>
   <si>
-    <t>2|12|1</t>
+    <t>2|10|1</t>
   </si>
   <si>
     <t>周杉事件三</t>
@@ -257,7 +257,7 @@
     <t>1|3|4</t>
   </si>
   <si>
-    <t>2|30|1</t>
+    <t>2|32|1</t>
   </si>
   <si>
     <t>温叙事件一</t>
@@ -284,6 +284,9 @@
     <t>1|6|2</t>
   </si>
   <si>
+    <t>2|16|1</t>
+  </si>
+  <si>
     <t>温叙事件四</t>
   </si>
   <si>
@@ -323,7 +326,7 @@
     <t>0_1</t>
   </si>
   <si>
-    <t>3|80|3</t>
+    <t>3|80|1</t>
   </si>
   <si>
     <t>传媒界的“无冕之王”</t>
@@ -332,7 +335,7 @@
     <t>0_2</t>
   </si>
   <si>
-    <t>4|100|3</t>
+    <t>4|100|1</t>
   </si>
   <si>
     <t>手握资本的“公关女王”</t>
@@ -341,13 +344,19 @@
     <t>0_3</t>
   </si>
   <si>
-    <t>2|100|3</t>
+    <t>2|100|1</t>
   </si>
   <si>
     <t>不被定义的自由</t>
   </si>
   <si>
     <t>0_4</t>
+  </si>
+  <si>
+    <t>岁月静好的观察者</t>
+  </si>
+  <si>
+    <t>0_5</t>
   </si>
 </sst>
 </file>
@@ -2031,7 +2040,7 @@
         <v>84</v>
       </c>
       <c r="I20" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="J20" t="s">
         <v>82</v>
@@ -2048,22 +2057,22 @@
         <v>2</v>
       </c>
       <c r="E21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F21">
         <v>1</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I21" t="s">
         <v>72</v>
       </c>
       <c r="J21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="2:10">
@@ -2077,22 +2086,22 @@
         <v>2</v>
       </c>
       <c r="E22" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F22">
         <v>1</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I22" t="s">
         <v>76</v>
       </c>
       <c r="J22" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="2:10">
@@ -2106,16 +2115,16 @@
         <v>2</v>
       </c>
       <c r="E23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F23">
         <v>1</v>
       </c>
       <c r="G23" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J23" t="s">
         <v>92</v>
-      </c>
-      <c r="J23" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="24" spans="2:10">
@@ -2135,7 +2144,7 @@
         <v>1</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J24" t="s">
         <v>4</v>
@@ -2152,16 +2161,16 @@
         <v>2</v>
       </c>
       <c r="E25" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="J25" t="s">
         <v>95</v>
-      </c>
-      <c r="J25" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="26" spans="2:10">
@@ -2172,19 +2181,19 @@
         <v>3</v>
       </c>
       <c r="E26" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F26">
         <v>0</v>
       </c>
       <c r="G26" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H26" t="s">
+        <v>99</v>
+      </c>
+      <c r="J26" t="s">
         <v>97</v>
-      </c>
-      <c r="H26" t="s">
-        <v>98</v>
-      </c>
-      <c r="J26" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="27" spans="2:10">
@@ -2195,19 +2204,19 @@
         <v>3</v>
       </c>
       <c r="E27" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F27">
         <v>0</v>
       </c>
       <c r="G27" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H27" t="s">
+        <v>102</v>
+      </c>
+      <c r="J27" t="s">
         <v>100</v>
-      </c>
-      <c r="H27" t="s">
-        <v>101</v>
-      </c>
-      <c r="J27" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="28" spans="2:10">
@@ -2218,19 +2227,19 @@
         <v>3</v>
       </c>
       <c r="E28" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F28">
         <v>0</v>
       </c>
       <c r="G28" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H28" t="s">
+        <v>105</v>
+      </c>
+      <c r="J28" t="s">
         <v>103</v>
-      </c>
-      <c r="H28" t="s">
-        <v>104</v>
-      </c>
-      <c r="J28" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="29" spans="2:10">
@@ -2241,19 +2250,19 @@
         <v>3</v>
       </c>
       <c r="E29" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F29">
         <v>0</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H29">
         <v>7</v>
       </c>
       <c r="J29" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="2:10">
@@ -2263,8 +2272,17 @@
       <c r="D30">
         <v>3</v>
       </c>
+      <c r="E30" t="s">
+        <v>108</v>
+      </c>
       <c r="F30">
         <v>0</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="J30" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Document/云熹约定项目文档/9.事件配置表/特殊事件配置表/特殊事件配置表.xlsx
+++ b/Assets/Document/云熹约定项目文档/9.事件配置表/特殊事件配置表/特殊事件配置表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="120">
   <si>
     <t>描述</t>
   </si>
@@ -41,276 +41,279 @@
     <t>事件类型</t>
   </si>
   <si>
+    <t>标题</t>
+  </si>
+  <si>
+    <t>消耗AP</t>
+  </si>
+  <si>
+    <t>事件标号</t>
+  </si>
+  <si>
+    <t>是否会显示（解锁条件）</t>
+  </si>
+  <si>
+    <t>是否能点击条件</t>
+  </si>
+  <si>
+    <t>剧情图名称</t>
+  </si>
+  <si>
+    <t>字段名</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>MapId</t>
+  </si>
+  <si>
+    <t>EventType</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>CostAP</t>
+  </si>
+  <si>
+    <t>EventNum</t>
+  </si>
+  <si>
+    <t>VisibleConditions</t>
+  </si>
+  <si>
+    <t>PlayableConditions</t>
+  </si>
+  <si>
+    <t>TargetGraphName</t>
+  </si>
+  <si>
+    <t>数据类型</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>居家</t>
+  </si>
+  <si>
+    <t>-1_1</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>去商场</t>
+  </si>
+  <si>
+    <t>-1_2</t>
+  </si>
+  <si>
+    <t>ShoppingMall</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>去医院</t>
+  </si>
+  <si>
+    <t>-1_4</t>
+  </si>
+  <si>
+    <t>Hospital</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>去公园</t>
+  </si>
+  <si>
+    <t>-1_5</t>
+  </si>
+  <si>
+    <t>Park</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>去书店</t>
+  </si>
+  <si>
+    <t>-1_6</t>
+  </si>
+  <si>
+    <t>BookStore</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>去游乐园</t>
+  </si>
+  <si>
+    <t>-1_7</t>
+  </si>
+  <si>
+    <t>AmusementPark</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>去电影院</t>
+  </si>
+  <si>
+    <t>-1_8</t>
+  </si>
+  <si>
+    <t>Cinema</t>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t>去美甲店</t>
+  </si>
+  <si>
+    <t>-1_9</t>
+  </si>
+  <si>
+    <t>NailSalon</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>去理发店</t>
+  </si>
+  <si>
+    <t>-1_10</t>
+  </si>
+  <si>
+    <t>BarberShop</t>
+  </si>
+  <si>
+    <t>周杉事件一</t>
+  </si>
+  <si>
+    <t>3_1</t>
+  </si>
+  <si>
+    <t>周杉事件二</t>
+  </si>
+  <si>
+    <t>3_2</t>
+  </si>
+  <si>
+    <t>1|3|1</t>
+  </si>
+  <si>
+    <t>2|10|1</t>
+  </si>
+  <si>
+    <t>周杉事件三</t>
+  </si>
+  <si>
+    <t>3_3</t>
+  </si>
+  <si>
+    <t>1|3|2</t>
+  </si>
+  <si>
+    <t>2|18|1</t>
+  </si>
+  <si>
+    <t>周杉事件四</t>
+  </si>
+  <si>
+    <t>3_4</t>
+  </si>
+  <si>
+    <t>1|3|3</t>
+  </si>
+  <si>
+    <t>2|24|1</t>
+  </si>
+  <si>
+    <t>周杉事件五</t>
+  </si>
+  <si>
+    <t>3_5</t>
+  </si>
+  <si>
+    <t>1|3|4</t>
+  </si>
+  <si>
+    <t>2|32|1</t>
+  </si>
+  <si>
+    <t>温叙事件一</t>
+  </si>
+  <si>
+    <t>6_1</t>
+  </si>
+  <si>
+    <t>温叙事件二</t>
+  </si>
+  <si>
+    <t>6_2</t>
+  </si>
+  <si>
+    <t>1|6|1</t>
+  </si>
+  <si>
+    <t>温叙事件三</t>
+  </si>
+  <si>
+    <t>6_3</t>
+  </si>
+  <si>
+    <t>1|6|2</t>
+  </si>
+  <si>
+    <t>2|16|1</t>
+  </si>
+  <si>
+    <t>温叙事件四</t>
+  </si>
+  <si>
+    <t>6_4</t>
+  </si>
+  <si>
+    <t>1|6|3</t>
+  </si>
+  <si>
+    <t>温叙事件五</t>
+  </si>
+  <si>
+    <t>6_5</t>
+  </si>
+  <si>
+    <t>1|6|4</t>
+  </si>
+  <si>
+    <t>陈予宁事件一</t>
+  </si>
+  <si>
+    <t>4_1</t>
+  </si>
+  <si>
     <t>陈予荣事件一</t>
   </si>
   <si>
-    <t>消耗AP</t>
-  </si>
-  <si>
-    <t>事件标号</t>
-  </si>
-  <si>
-    <t>是否会显示（解锁条件）</t>
-  </si>
-  <si>
-    <t>是否能点击条件</t>
-  </si>
-  <si>
-    <t>剧情图名称</t>
-  </si>
-  <si>
-    <t>字段名</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>MapId</t>
-  </si>
-  <si>
-    <t>EventType</t>
-  </si>
-  <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t>CostAP</t>
-  </si>
-  <si>
-    <t>EventNum</t>
-  </si>
-  <si>
-    <t>VisibleConditions</t>
-  </si>
-  <si>
-    <t>PlayableConditions</t>
-  </si>
-  <si>
-    <t>TargetGraphName</t>
-  </si>
-  <si>
-    <t>数据类型</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>01</t>
-  </si>
-  <si>
-    <t>居家</t>
-  </si>
-  <si>
-    <t>-1_1</t>
-  </si>
-  <si>
-    <t>Home</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>去商场</t>
-  </si>
-  <si>
-    <t>-1_2</t>
-  </si>
-  <si>
-    <t>ShoppingMall</t>
-  </si>
-  <si>
-    <t>03</t>
-  </si>
-  <si>
-    <t>去医院</t>
-  </si>
-  <si>
-    <t>-1_4</t>
-  </si>
-  <si>
-    <t>Hospital</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>去公园</t>
-  </si>
-  <si>
-    <t>-1_5</t>
-  </si>
-  <si>
-    <t>Park</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>去书店</t>
-  </si>
-  <si>
-    <t>-1_6</t>
-  </si>
-  <si>
-    <t>BookStore</t>
-  </si>
-  <si>
-    <t>06</t>
-  </si>
-  <si>
-    <t>去游乐园</t>
-  </si>
-  <si>
-    <t>-1_7</t>
-  </si>
-  <si>
-    <t>AmusementPark</t>
-  </si>
-  <si>
-    <t>07</t>
-  </si>
-  <si>
-    <t>去电影院</t>
-  </si>
-  <si>
-    <t>-1_8</t>
-  </si>
-  <si>
-    <t>Cinema</t>
-  </si>
-  <si>
-    <t>08</t>
-  </si>
-  <si>
-    <t>去美甲店</t>
-  </si>
-  <si>
-    <t>-1_9</t>
-  </si>
-  <si>
-    <t>NailSalon</t>
-  </si>
-  <si>
-    <t>09</t>
-  </si>
-  <si>
-    <t>去理发店</t>
-  </si>
-  <si>
-    <t>-1_10</t>
-  </si>
-  <si>
-    <t>BarberShop</t>
-  </si>
-  <si>
-    <t>周杉事件一</t>
-  </si>
-  <si>
-    <t>3_1</t>
-  </si>
-  <si>
-    <t>周杉事件二</t>
-  </si>
-  <si>
-    <t>3_2</t>
-  </si>
-  <si>
-    <t>1|3|1</t>
-  </si>
-  <si>
-    <t>2|10|1</t>
-  </si>
-  <si>
-    <t>周杉事件三</t>
-  </si>
-  <si>
-    <t>3_3</t>
-  </si>
-  <si>
-    <t>1|3|2</t>
-  </si>
-  <si>
-    <t>2|18|1</t>
-  </si>
-  <si>
-    <t>周杉事件四</t>
-  </si>
-  <si>
-    <t>3_4</t>
-  </si>
-  <si>
-    <t>1|3|3</t>
-  </si>
-  <si>
-    <t>2|24|1</t>
-  </si>
-  <si>
-    <t>周杉事件五</t>
-  </si>
-  <si>
-    <t>3_5</t>
-  </si>
-  <si>
-    <t>1|3|4</t>
-  </si>
-  <si>
-    <t>2|32|1</t>
-  </si>
-  <si>
-    <t>温叙事件一</t>
-  </si>
-  <si>
-    <t>6_1</t>
-  </si>
-  <si>
-    <t>温叙事件二</t>
-  </si>
-  <si>
-    <t>6_2</t>
-  </si>
-  <si>
-    <t>1|6|1</t>
-  </si>
-  <si>
-    <t>温叙事件三</t>
-  </si>
-  <si>
-    <t>6_3</t>
-  </si>
-  <si>
-    <t>1|6|2</t>
-  </si>
-  <si>
-    <t>2|16|1</t>
-  </si>
-  <si>
-    <t>温叙事件四</t>
-  </si>
-  <si>
-    <t>6_4</t>
-  </si>
-  <si>
-    <t>1|6|3</t>
-  </si>
-  <si>
-    <t>温叙事件五</t>
-  </si>
-  <si>
-    <t>6_5</t>
-  </si>
-  <si>
-    <t>1|6|4</t>
-  </si>
-  <si>
-    <t>陈予宁事件一</t>
-  </si>
-  <si>
-    <t>4_1</t>
-  </si>
-  <si>
     <t>5_1</t>
   </si>
   <si>
@@ -357,6 +360,33 @@
   </si>
   <si>
     <t>0_5</t>
+  </si>
+  <si>
+    <t>周杉80单线</t>
+  </si>
+  <si>
+    <t>0_6</t>
+  </si>
+  <si>
+    <t>6|3|80|1</t>
+  </si>
+  <si>
+    <t>温叙80单线</t>
+  </si>
+  <si>
+    <t>0_7</t>
+  </si>
+  <si>
+    <t>6|6|80|1</t>
+  </si>
+  <si>
+    <t>周杉&amp;温叙1</t>
+  </si>
+  <si>
+    <t>0_8</t>
+  </si>
+  <si>
+    <t>6|3|80|1,6|6|80|1</t>
   </si>
 </sst>
 </file>
@@ -1510,7 +1540,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="3" width="8.875" customWidth="1"/>
@@ -2138,16 +2168,16 @@
         <v>2</v>
       </c>
       <c r="E24" t="s">
-        <v>4</v>
+        <v>94</v>
       </c>
       <c r="F24">
         <v>1</v>
       </c>
       <c r="G24" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="J24" t="s">
         <v>94</v>
-      </c>
-      <c r="J24" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="25" spans="2:10">
@@ -2161,16 +2191,16 @@
         <v>2</v>
       </c>
       <c r="E25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="J25" t="s">
         <v>96</v>
-      </c>
-      <c r="J25" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="26" spans="2:10">
@@ -2181,19 +2211,19 @@
         <v>3</v>
       </c>
       <c r="E26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F26">
         <v>0</v>
       </c>
       <c r="G26" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="H26" t="s">
+        <v>100</v>
+      </c>
+      <c r="J26" t="s">
         <v>98</v>
-      </c>
-      <c r="H26" t="s">
-        <v>99</v>
-      </c>
-      <c r="J26" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="27" spans="2:10">
@@ -2204,19 +2234,19 @@
         <v>3</v>
       </c>
       <c r="E27" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F27">
         <v>0</v>
       </c>
       <c r="G27" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H27" t="s">
+        <v>103</v>
+      </c>
+      <c r="J27" t="s">
         <v>101</v>
-      </c>
-      <c r="H27" t="s">
-        <v>102</v>
-      </c>
-      <c r="J27" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="28" spans="2:10">
@@ -2227,19 +2257,19 @@
         <v>3</v>
       </c>
       <c r="E28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F28">
         <v>0</v>
       </c>
       <c r="G28" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H28" t="s">
+        <v>106</v>
+      </c>
+      <c r="J28" t="s">
         <v>104</v>
-      </c>
-      <c r="H28" t="s">
-        <v>105</v>
-      </c>
-      <c r="J28" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="29" spans="2:10">
@@ -2250,19 +2280,19 @@
         <v>3</v>
       </c>
       <c r="E29" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F29">
         <v>0</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H29">
         <v>7</v>
       </c>
       <c r="J29" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" spans="2:10">
@@ -2273,16 +2303,85 @@
         <v>3</v>
       </c>
       <c r="E30" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F30">
         <v>0</v>
       </c>
       <c r="G30" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="J30" t="s">
         <v>109</v>
       </c>
-      <c r="J30" t="s">
-        <v>108</v>
+    </row>
+    <row r="31" spans="2:10">
+      <c r="B31">
+        <v>28</v>
+      </c>
+      <c r="D31">
+        <v>3</v>
+      </c>
+      <c r="E31" t="s">
+        <v>111</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H31" t="s">
+        <v>113</v>
+      </c>
+      <c r="J31" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10">
+      <c r="B32">
+        <v>29</v>
+      </c>
+      <c r="D32">
+        <v>3</v>
+      </c>
+      <c r="E32" t="s">
+        <v>114</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H32" t="s">
+        <v>116</v>
+      </c>
+      <c r="J32" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10">
+      <c r="B33">
+        <v>30</v>
+      </c>
+      <c r="D33">
+        <v>3</v>
+      </c>
+      <c r="E33" t="s">
+        <v>117</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H33" t="s">
+        <v>119</v>
+      </c>
+      <c r="J33" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Document/云熹约定项目文档/9.事件配置表/特殊事件配置表/特殊事件配置表.xlsx
+++ b/Assets/Document/云熹约定项目文档/9.事件配置表/特殊事件配置表/特殊事件配置表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="46">
   <si>
     <t>描述</t>
   </si>
@@ -101,201 +101,57 @@
     <t>01</t>
   </si>
   <si>
-    <t>居家</t>
-  </si>
-  <si>
-    <t>-1_1</t>
-  </si>
-  <si>
-    <t>Home</t>
+    <t>周杉事件一</t>
+  </si>
+  <si>
+    <t>3_1</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>温叙事件一</t>
+  </si>
+  <si>
+    <t>6_1</t>
   </si>
   <si>
     <t>02</t>
   </si>
   <si>
-    <t>去商场</t>
-  </si>
-  <si>
-    <t>-1_2</t>
-  </si>
-  <si>
-    <t>ShoppingMall</t>
+    <t>温叙事件二</t>
+  </si>
+  <si>
+    <t>6_2</t>
+  </si>
+  <si>
+    <t>1|6|1</t>
+  </si>
+  <si>
+    <t>温叙事件三</t>
+  </si>
+  <si>
+    <t>6_3</t>
+  </si>
+  <si>
+    <t>1|6|2</t>
   </si>
   <si>
     <t>03</t>
   </si>
   <si>
-    <t>去医院</t>
-  </si>
-  <si>
-    <t>-1_4</t>
-  </si>
-  <si>
-    <t>Hospital</t>
+    <t>温叙事件四</t>
+  </si>
+  <si>
+    <t>6_4</t>
+  </si>
+  <si>
+    <t>1|6|3</t>
   </si>
   <si>
     <t>04</t>
   </si>
   <si>
-    <t>去公园</t>
-  </si>
-  <si>
-    <t>-1_5</t>
-  </si>
-  <si>
-    <t>Park</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>去书店</t>
-  </si>
-  <si>
-    <t>-1_6</t>
-  </si>
-  <si>
-    <t>BookStore</t>
-  </si>
-  <si>
-    <t>06</t>
-  </si>
-  <si>
-    <t>去游乐园</t>
-  </si>
-  <si>
-    <t>-1_7</t>
-  </si>
-  <si>
-    <t>AmusementPark</t>
-  </si>
-  <si>
-    <t>07</t>
-  </si>
-  <si>
-    <t>去电影院</t>
-  </si>
-  <si>
-    <t>-1_8</t>
-  </si>
-  <si>
-    <t>Cinema</t>
-  </si>
-  <si>
-    <t>08</t>
-  </si>
-  <si>
-    <t>去美甲店</t>
-  </si>
-  <si>
-    <t>-1_9</t>
-  </si>
-  <si>
-    <t>NailSalon</t>
-  </si>
-  <si>
-    <t>09</t>
-  </si>
-  <si>
-    <t>去理发店</t>
-  </si>
-  <si>
-    <t>-1_10</t>
-  </si>
-  <si>
-    <t>BarberShop</t>
-  </si>
-  <si>
-    <t>周杉事件一</t>
-  </si>
-  <si>
-    <t>3_1</t>
-  </si>
-  <si>
-    <t>周杉事件二</t>
-  </si>
-  <si>
-    <t>3_2</t>
-  </si>
-  <si>
-    <t>1|3|1</t>
-  </si>
-  <si>
-    <t>2|10|1</t>
-  </si>
-  <si>
-    <t>周杉事件三</t>
-  </si>
-  <si>
-    <t>3_3</t>
-  </si>
-  <si>
-    <t>1|3|2</t>
-  </si>
-  <si>
-    <t>2|18|1</t>
-  </si>
-  <si>
-    <t>周杉事件四</t>
-  </si>
-  <si>
-    <t>3_4</t>
-  </si>
-  <si>
-    <t>1|3|3</t>
-  </si>
-  <si>
-    <t>2|24|1</t>
-  </si>
-  <si>
-    <t>周杉事件五</t>
-  </si>
-  <si>
-    <t>3_5</t>
-  </si>
-  <si>
-    <t>1|3|4</t>
-  </si>
-  <si>
-    <t>2|32|1</t>
-  </si>
-  <si>
-    <t>温叙事件一</t>
-  </si>
-  <si>
-    <t>6_1</t>
-  </si>
-  <si>
-    <t>温叙事件二</t>
-  </si>
-  <si>
-    <t>6_2</t>
-  </si>
-  <si>
-    <t>1|6|1</t>
-  </si>
-  <si>
-    <t>温叙事件三</t>
-  </si>
-  <si>
-    <t>6_3</t>
-  </si>
-  <si>
-    <t>1|6|2</t>
-  </si>
-  <si>
-    <t>2|16|1</t>
-  </si>
-  <si>
-    <t>温叙事件四</t>
-  </si>
-  <si>
-    <t>6_4</t>
-  </si>
-  <si>
-    <t>1|6|3</t>
-  </si>
-  <si>
     <t>温叙事件五</t>
   </si>
   <si>
@@ -305,88 +161,10 @@
     <t>1|6|4</t>
   </si>
   <si>
-    <t>陈予宁事件一</t>
-  </si>
-  <si>
-    <t>4_1</t>
-  </si>
-  <si>
     <t>陈予荣事件一</t>
   </si>
   <si>
     <t>5_1</t>
-  </si>
-  <si>
-    <t>何行舟事件一</t>
-  </si>
-  <si>
-    <t>7_1</t>
-  </si>
-  <si>
-    <t>现象级造梦师</t>
-  </si>
-  <si>
-    <t>0_1</t>
-  </si>
-  <si>
-    <t>3|80|1</t>
-  </si>
-  <si>
-    <t>传媒界的“无冕之王”</t>
-  </si>
-  <si>
-    <t>0_2</t>
-  </si>
-  <si>
-    <t>4|100|1</t>
-  </si>
-  <si>
-    <t>手握资本的“公关女王”</t>
-  </si>
-  <si>
-    <t>0_3</t>
-  </si>
-  <si>
-    <t>2|100|1</t>
-  </si>
-  <si>
-    <t>不被定义的自由</t>
-  </si>
-  <si>
-    <t>0_4</t>
-  </si>
-  <si>
-    <t>岁月静好的观察者</t>
-  </si>
-  <si>
-    <t>0_5</t>
-  </si>
-  <si>
-    <t>周杉80单线</t>
-  </si>
-  <si>
-    <t>0_6</t>
-  </si>
-  <si>
-    <t>6|3|80|1</t>
-  </si>
-  <si>
-    <t>温叙80单线</t>
-  </si>
-  <si>
-    <t>0_7</t>
-  </si>
-  <si>
-    <t>6|6|80|1</t>
-  </si>
-  <si>
-    <t>周杉&amp;温叙1</t>
-  </si>
-  <si>
-    <t>0_8</t>
-  </si>
-  <si>
-    <t>6|3|80|1,6|6|80|1</t>
   </si>
 </sst>
 </file>
@@ -1010,9 +788,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1540,7 +1315,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="3" width="8.875" customWidth="1"/>
@@ -1657,7 +1432,7 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="s">
         <v>24</v>
@@ -1665,11 +1440,11 @@
       <c r="F4">
         <v>1</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="1" t="s">
         <v>25</v>
       </c>
       <c r="J4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -1677,22 +1452,22 @@
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" t="s">
         <v>27</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>28</v>
       </c>
       <c r="F5">
         <v>1</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>29</v>
+      <c r="G5" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="J5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -1700,22 +1475,26 @@
         <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>33</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="H6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6"/>
       <c r="J6" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -1723,22 +1502,26 @@
         <v>4</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>37</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="H7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7"/>
       <c r="J7" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1746,22 +1529,26 @@
         <v>5</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F8">
         <v>1</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>41</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="H8" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8"/>
       <c r="J8" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1769,22 +1556,26 @@
         <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>45</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="H9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I9"/>
       <c r="J9" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -1792,596 +1583,22 @@
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F10">
         <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="J10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="B11">
-        <v>8</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11" t="s">
-        <v>52</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="B12">
-        <v>9</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12" t="s">
-        <v>56</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="J12" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="B13">
-        <v>10</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13">
-        <v>2</v>
-      </c>
-      <c r="E13" t="s">
-        <v>59</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="J13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="B14">
-        <v>11</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14">
-        <v>2</v>
-      </c>
-      <c r="E14" t="s">
-        <v>61</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H14" t="s">
-        <v>63</v>
-      </c>
-      <c r="I14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J14" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="B15">
-        <v>12</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15">
-        <v>2</v>
-      </c>
-      <c r="E15" t="s">
-        <v>65</v>
-      </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="H15" t="s">
-        <v>67</v>
-      </c>
-      <c r="I15" t="s">
-        <v>68</v>
-      </c>
-      <c r="J15" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="B16">
-        <v>13</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16">
-        <v>2</v>
-      </c>
-      <c r="E16" t="s">
-        <v>69</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="H16" t="s">
-        <v>71</v>
-      </c>
-      <c r="I16" t="s">
-        <v>72</v>
-      </c>
-      <c r="J16" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10">
-      <c r="B17">
-        <v>14</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17">
-        <v>2</v>
-      </c>
-      <c r="E17" t="s">
-        <v>73</v>
-      </c>
-      <c r="F17">
-        <v>1</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="H17" t="s">
-        <v>75</v>
-      </c>
-      <c r="I17" t="s">
-        <v>76</v>
-      </c>
-      <c r="J17" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="18" spans="2:10">
-      <c r="B18">
-        <v>15</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D18">
-        <v>2</v>
-      </c>
-      <c r="E18" t="s">
-        <v>77</v>
-      </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J18" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="19" spans="2:10">
-      <c r="B19">
-        <v>16</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D19">
-        <v>2</v>
-      </c>
-      <c r="E19" t="s">
-        <v>79</v>
-      </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="H19" t="s">
-        <v>81</v>
-      </c>
-      <c r="I19" t="s">
-        <v>64</v>
-      </c>
-      <c r="J19" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="20" spans="2:10">
-      <c r="B20">
-        <v>17</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20">
-        <v>2</v>
-      </c>
-      <c r="E20" t="s">
-        <v>82</v>
-      </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="H20" t="s">
-        <v>84</v>
-      </c>
-      <c r="I20" t="s">
-        <v>85</v>
-      </c>
-      <c r="J20" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10">
-      <c r="B21">
-        <v>18</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D21">
-        <v>2</v>
-      </c>
-      <c r="E21" t="s">
-        <v>86</v>
-      </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="H21" t="s">
-        <v>88</v>
-      </c>
-      <c r="I21" t="s">
-        <v>72</v>
-      </c>
-      <c r="J21" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="22" spans="2:10">
-      <c r="B22">
-        <v>19</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D22">
-        <v>2</v>
-      </c>
-      <c r="E22" t="s">
-        <v>89</v>
-      </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="H22" t="s">
-        <v>91</v>
-      </c>
-      <c r="I22" t="s">
-        <v>76</v>
-      </c>
-      <c r="J22" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="23" spans="2:10">
-      <c r="B23">
-        <v>20</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D23">
-        <v>2</v>
-      </c>
-      <c r="E23" t="s">
-        <v>92</v>
-      </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="J23" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10">
-      <c r="B24">
-        <v>21</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D24">
-        <v>2</v>
-      </c>
-      <c r="E24" t="s">
-        <v>94</v>
-      </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="J24" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="25" spans="2:10">
-      <c r="B25">
-        <v>22</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D25">
-        <v>2</v>
-      </c>
-      <c r="E25" t="s">
-        <v>96</v>
-      </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="J25" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="26" spans="2:10">
-      <c r="B26">
-        <v>23</v>
-      </c>
-      <c r="D26">
-        <v>3</v>
-      </c>
-      <c r="E26" t="s">
-        <v>98</v>
-      </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="H26" t="s">
-        <v>100</v>
-      </c>
-      <c r="J26" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="27" spans="2:10">
-      <c r="B27">
-        <v>24</v>
-      </c>
-      <c r="D27">
-        <v>3</v>
-      </c>
-      <c r="E27" t="s">
-        <v>101</v>
-      </c>
-      <c r="F27">
-        <v>0</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="H27" t="s">
-        <v>103</v>
-      </c>
-      <c r="J27" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="28" spans="2:10">
-      <c r="B28">
-        <v>25</v>
-      </c>
-      <c r="D28">
-        <v>3</v>
-      </c>
-      <c r="E28" t="s">
-        <v>104</v>
-      </c>
-      <c r="F28">
-        <v>0</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="H28" t="s">
-        <v>106</v>
-      </c>
-      <c r="J28" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10">
-      <c r="B29">
-        <v>26</v>
-      </c>
-      <c r="D29">
-        <v>3</v>
-      </c>
-      <c r="E29" t="s">
-        <v>107</v>
-      </c>
-      <c r="F29">
-        <v>0</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="H29">
-        <v>7</v>
-      </c>
-      <c r="J29" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="30" spans="2:10">
-      <c r="B30">
-        <v>27</v>
-      </c>
-      <c r="D30">
-        <v>3</v>
-      </c>
-      <c r="E30" t="s">
-        <v>109</v>
-      </c>
-      <c r="F30">
-        <v>0</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="J30" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10">
-      <c r="B31">
-        <v>28</v>
-      </c>
-      <c r="D31">
-        <v>3</v>
-      </c>
-      <c r="E31" t="s">
-        <v>111</v>
-      </c>
-      <c r="F31">
-        <v>0</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H31" t="s">
-        <v>113</v>
-      </c>
-      <c r="J31" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="32" spans="2:10">
-      <c r="B32">
-        <v>29</v>
-      </c>
-      <c r="D32">
-        <v>3</v>
-      </c>
-      <c r="E32" t="s">
-        <v>114</v>
-      </c>
-      <c r="F32">
-        <v>0</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="H32" t="s">
-        <v>116</v>
-      </c>
-      <c r="J32" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="33" spans="2:10">
-      <c r="B33">
-        <v>30</v>
-      </c>
-      <c r="D33">
-        <v>3</v>
-      </c>
-      <c r="E33" t="s">
-        <v>117</v>
-      </c>
-      <c r="F33">
-        <v>0</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="H33" t="s">
-        <v>119</v>
-      </c>
-      <c r="J33" t="s">
-        <v>117</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
